--- a/benchmarks_tests/FINAL_Benchmarks_for_paper/PyFock_scaling_behavior_GPU_SAO.xlsx
+++ b/benchmarks_tests/FINAL_Benchmarks_for_paper/PyFock_scaling_behavior_GPU_SAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manas/Documents/PyFock/benchmarks_tests/FINAL_Benchmarks_for_paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7794617-A7D3-394F-BD27-79C8326DE21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EEB022-51E6-CD42-8249-4BBFEF11CF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="16740" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
+    <workbookView xWindow="11380" yWindow="3860" windowWidth="28040" windowHeight="16740" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -304,6 +304,27 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="2">
+                  <c:v>0.18307692307692308</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.40384615384615385</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.70733333333333326</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2593749999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.7888235294117645</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.65625</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.4428571428571413</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -394,6 +415,27 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="2">
+                  <c:v>5.2307692307692312E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15076923076923077</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.29533333333333334</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.59812500000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.4447058823529411</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.7056249999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.0992857142857142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -484,6 +526,27 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="2">
+                  <c:v>8.1538461538461546E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15923076923076923</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.39750000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.74411764705882355</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0225</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.5685714285714287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -984,6 +1047,27 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="2">
+                  <c:v>0.18307692307692308</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.40384615384615385</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.70733333333333326</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2593749999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.7888235294117645</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.65625</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.4428571428571413</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1074,6 +1158,27 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="2">
+                  <c:v>5.2307692307692312E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15076923076923077</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.29533333333333334</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.59812500000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.4447058823529411</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.7056249999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.0992857142857142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1164,6 +1269,27 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="2">
+                  <c:v>8.1538461538461546E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15923076923076923</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.39750000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.74411764705882355</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0225</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.5685714285714287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -3086,26 +3212,21 @@
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7">
-        <v>25</v>
-      </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1">
-        <v>8</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="1"/>
+      <c r="G7" t="e">
         <f>C7/F7</f>
-        <v>0</v>
-      </c>
-      <c r="H7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H7" t="e">
         <f>D7/F7</f>
-        <v>0</v>
-      </c>
-      <c r="I7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I7" t="e">
         <f>E7/F7</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -3113,25 +3234,23 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1">
-        <v>10</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="1"/>
+      <c r="G8" t="e">
         <f t="shared" ref="G8:G15" si="0">C8/F8</f>
-        <v>0</v>
-      </c>
-      <c r="H8">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H8" t="e">
         <f t="shared" ref="H8:H15" si="1">D8/F8</f>
-        <v>0</v>
-      </c>
-      <c r="I8">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I8" t="e">
         <f t="shared" ref="I8:I15" si="2">E8/F8</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -3139,25 +3258,31 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>250</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+        <v>240</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.38</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1.06</v>
+      </c>
       <c r="F9" s="1">
         <v>13</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.18307692307692308</v>
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.2307692307692312E-2</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.1538461538461546E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -3165,25 +3290,31 @@
         <v>20</v>
       </c>
       <c r="B10">
-        <v>500</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+        <v>480</v>
+      </c>
+      <c r="C10" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.96</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2.0699999999999998</v>
+      </c>
       <c r="F10" s="1">
         <v>13</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.40384615384615385</v>
       </c>
       <c r="H10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.15076923076923077</v>
       </c>
       <c r="I10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.15923076923076923</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -3191,25 +3322,31 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>800</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+        <v>768</v>
+      </c>
+      <c r="C11" s="1">
+        <v>10.61</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4.43</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3.84</v>
+      </c>
       <c r="F11" s="1">
         <v>15</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.70733333333333326</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="I11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.25600000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -3217,25 +3354,31 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>1175</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+        <v>1128</v>
+      </c>
+      <c r="C12" s="1">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9.57</v>
+      </c>
+      <c r="E12" s="1">
+        <v>6.36</v>
+      </c>
       <c r="F12" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.2593749999999999</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.59812500000000002</v>
       </c>
       <c r="I12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.39750000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -3243,25 +3386,31 @@
         <v>76</v>
       </c>
       <c r="B13">
-        <v>1900</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+        <v>1824</v>
+      </c>
+      <c r="C13" s="1">
+        <v>47.41</v>
+      </c>
+      <c r="D13" s="1">
+        <v>24.56</v>
+      </c>
+      <c r="E13" s="1">
+        <v>12.65</v>
+      </c>
       <c r="F13" s="1">
         <v>17</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.7888235294117645</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.4447058823529411</v>
       </c>
       <c r="I13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.74411764705882355</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -3269,25 +3418,31 @@
         <v>100</v>
       </c>
       <c r="B14">
-        <v>2500</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+        <v>2400</v>
+      </c>
+      <c r="C14" s="1">
+        <v>74.5</v>
+      </c>
+      <c r="D14" s="1">
+        <v>43.29</v>
+      </c>
+      <c r="E14" s="1">
+        <v>16.36</v>
+      </c>
       <c r="F14" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.65625</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.7056249999999999</v>
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.0225</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -3295,25 +3450,31 @@
         <v>139</v>
       </c>
       <c r="B15">
-        <v>3475</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+        <v>3336</v>
+      </c>
+      <c r="C15" s="1">
+        <v>132.19999999999999</v>
+      </c>
+      <c r="D15" s="1">
+        <v>85.39</v>
+      </c>
+      <c r="E15" s="1">
+        <v>21.96</v>
+      </c>
       <c r="F15" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.4428571428571413</v>
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.0992857142857142</v>
       </c>
       <c r="I15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.5685714285714287</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -3362,56 +3523,182 @@
       <c r="A22">
         <v>10</v>
       </c>
+      <c r="B22">
+        <v>0.18307692307692308</v>
+      </c>
+      <c r="C22">
+        <v>5.2307692307692312E-2</v>
+      </c>
+      <c r="D22">
+        <v>8.1538461538461546E-2</v>
+      </c>
       <c r="G22">
         <v>250</v>
+      </c>
+      <c r="H22">
+        <v>0.18307692307692308</v>
+      </c>
+      <c r="I22">
+        <v>5.2307692307692312E-2</v>
+      </c>
+      <c r="J22">
+        <v>8.1538461538461546E-2</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>20</v>
       </c>
+      <c r="B23">
+        <v>0.40384615384615385</v>
+      </c>
+      <c r="C23">
+        <v>0.15076923076923077</v>
+      </c>
+      <c r="D23">
+        <v>0.15923076923076923</v>
+      </c>
       <c r="G23">
         <v>500</v>
+      </c>
+      <c r="H23">
+        <v>0.40384615384615385</v>
+      </c>
+      <c r="I23">
+        <v>0.15076923076923077</v>
+      </c>
+      <c r="J23">
+        <v>0.15923076923076923</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>32</v>
       </c>
+      <c r="B24">
+        <v>0.70733333333333326</v>
+      </c>
+      <c r="C24">
+        <v>0.29533333333333334</v>
+      </c>
+      <c r="D24">
+        <v>0.25600000000000001</v>
+      </c>
       <c r="G24">
         <v>800</v>
+      </c>
+      <c r="H24">
+        <v>0.70733333333333326</v>
+      </c>
+      <c r="I24">
+        <v>0.29533333333333334</v>
+      </c>
+      <c r="J24">
+        <v>0.25600000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>47</v>
       </c>
+      <c r="B25">
+        <v>1.2593749999999999</v>
+      </c>
+      <c r="C25">
+        <v>0.59812500000000002</v>
+      </c>
+      <c r="D25">
+        <v>0.39750000000000002</v>
+      </c>
       <c r="G25">
         <v>1175</v>
+      </c>
+      <c r="H25">
+        <v>1.2593749999999999</v>
+      </c>
+      <c r="I25">
+        <v>0.59812500000000002</v>
+      </c>
+      <c r="J25">
+        <v>0.39750000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>76</v>
       </c>
+      <c r="B26">
+        <v>2.7888235294117645</v>
+      </c>
+      <c r="C26">
+        <v>1.4447058823529411</v>
+      </c>
+      <c r="D26">
+        <v>0.74411764705882355</v>
+      </c>
       <c r="G26">
         <v>1900</v>
+      </c>
+      <c r="H26">
+        <v>2.7888235294117645</v>
+      </c>
+      <c r="I26">
+        <v>1.4447058823529411</v>
+      </c>
+      <c r="J26">
+        <v>0.74411764705882355</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>100</v>
       </c>
+      <c r="B27">
+        <v>4.65625</v>
+      </c>
+      <c r="C27">
+        <v>2.7056249999999999</v>
+      </c>
+      <c r="D27">
+        <v>1.0225</v>
+      </c>
       <c r="G27">
         <v>2500</v>
+      </c>
+      <c r="H27">
+        <v>4.65625</v>
+      </c>
+      <c r="I27">
+        <v>2.7056249999999999</v>
+      </c>
+      <c r="J27">
+        <v>1.0225</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>139</v>
       </c>
+      <c r="B28">
+        <v>9.4428571428571413</v>
+      </c>
+      <c r="C28">
+        <v>6.0992857142857142</v>
+      </c>
+      <c r="D28">
+        <v>1.5685714285714287</v>
+      </c>
       <c r="G28">
         <v>3475</v>
+      </c>
+      <c r="H28">
+        <v>9.4428571428571413</v>
+      </c>
+      <c r="I28">
+        <v>6.0992857142857142</v>
+      </c>
+      <c r="J28">
+        <v>1.5685714285714287</v>
       </c>
     </row>
   </sheetData>

--- a/benchmarks_tests/FINAL_Benchmarks_for_paper/PyFock_scaling_behavior_GPU_SAO.xlsx
+++ b/benchmarks_tests/FINAL_Benchmarks_for_paper/PyFock_scaling_behavior_GPU_SAO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manas/Documents/PyFock/benchmarks_tests/FINAL_Benchmarks_for_paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EEB022-51E6-CD42-8249-4BBFEF11CF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB78C6B-7A47-B248-B7BF-B835E4A618A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11380" yWindow="3860" windowWidth="28040" windowHeight="16740" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
+    <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="16740" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
